--- a/data/nzd0596/nzd0596.xlsx
+++ b/data/nzd0596/nzd0596.xlsx
@@ -23825,9 +23825,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0883</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -23875,9 +23881,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1167</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -23925,9 +23937,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0876</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -23975,9 +23993,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -24025,9 +24049,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -24075,9 +24105,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -24125,9 +24161,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -24175,9 +24217,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -24225,9 +24273,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -24275,9 +24329,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -24325,9 +24385,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -24375,9 +24441,15 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -24425,9 +24497,15 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -24475,9 +24553,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -24525,9 +24609,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -24575,9 +24665,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -24625,9 +24721,15 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -24675,9 +24777,15 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -24725,9 +24833,15 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -24775,9 +24889,15 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1192</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -24825,9 +24945,15 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -24875,9 +25001,15 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -24925,9 +25057,15 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -24975,9 +25113,15 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -25025,9 +25169,15 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1592</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -25075,9 +25225,15 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -25125,9 +25281,15 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -25175,9 +25337,15 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -25225,9 +25393,15 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -25275,9 +25449,15 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -25325,9 +25505,15 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -25375,9 +25561,15 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -25425,9 +25617,15 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -25475,9 +25673,15 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -25525,9 +25729,15 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1671</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -25575,9 +25785,15 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -25625,9 +25841,15 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -25675,9 +25897,15 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -25725,9 +25953,15 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.1529</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -25775,9 +26009,15 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -25825,9 +26065,15 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -25875,9 +26121,15 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -25925,9 +26177,15 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1723</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -25975,9 +26233,15 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -26025,9 +26289,15 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -26075,9 +26345,15 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -26125,9 +26401,15 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -26175,9 +26457,15 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -26225,9 +26513,15 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -26275,9 +26569,15 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -26325,9 +26625,15 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="F52" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.1293</v>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -26375,9 +26681,15 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -26425,9 +26737,15 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -26475,9 +26793,15 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="F55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.1492</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -26525,9 +26849,15 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0951</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1756</v>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -26575,9 +26905,15 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="F57" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.1104</v>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -26625,9 +26961,15 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.1052</v>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -26675,9 +27017,15 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.0822</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1271</v>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -26725,9 +27073,15 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.1618</v>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -26775,9 +27129,15 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.1192</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.19</v>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -26825,9 +27185,15 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -26875,9 +27241,15 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -26925,9 +27297,15 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.1942</v>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -26975,9 +27353,15 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.1273</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.1905</v>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -27025,9 +27409,15 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.1816</v>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
